--- a/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_mtd_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_mtd_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -158,12 +158,24 @@
     <t xml:space="preserve">3</t>
   </si>
   <si>
+    <t xml:space="preserve">LC_149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1bis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THU_BL_LOC</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC_151</t>
   </si>
   <si>
-    <t xml:space="preserve">1bis</t>
-  </si>
-  <si>
     <t xml:space="preserve">LC_152</t>
   </si>
   <si>
@@ -239,118 +251,127 @@
     <t xml:space="preserve">MS_016</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_017</t>
+    <t xml:space="preserve">MS_019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIL_ST_INF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIL_ST_MDB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artific_Inf_Fruits_5_6days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FruitLayedIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAR_BL_LOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat_Inf_Fruits_5_6days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FruitJuice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat_Inf_Fruits_Focal_Sites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_185</t>
   </si>
   <si>
     <t xml:space="preserve">DRE</t>
   </si>
   <si>
     <t xml:space="preserve">IST_ST_DRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIL_ST_INF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIL_ST_MDB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artific_Inf_Fruits_5_6days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FruitLayedIn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CEC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat_Inf_Fruits_5_6days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FruitJuice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat_Inf_Fruits_Focal_Sites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_185</t>
   </si>
   <si>
     <t xml:space="preserve">MS_186</t>
@@ -1166,16 +1187,16 @@
         <v>27</v>
       </c>
       <c r="J8" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="N8" t="s">
         <v>32</v>
@@ -1198,7 +1219,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
         <v>49</v>
@@ -1228,13 +1249,13 @@
         <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
       </c>
       <c r="M9" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N9" t="s">
         <v>32</v>
@@ -1252,12 +1273,12 @@
         <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
@@ -1269,7 +1290,7 @@
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
@@ -1284,16 +1305,16 @@
         <v>27</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L10" t="s">
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N10" t="s">
         <v>32</v>
@@ -1311,15 +1332,15 @@
         <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
@@ -1343,16 +1364,16 @@
         <v>27</v>
       </c>
       <c r="J11" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K11" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L11" t="s">
         <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="N11" t="s">
         <v>32</v>
@@ -1370,24 +1391,24 @@
         <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
         <v>24</v>
@@ -1405,36 +1426,36 @@
         <v>28</v>
       </c>
       <c r="K12" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R12" t="s">
+        <v>34</v>
+      </c>
+      <c r="S12" t="s">
         <v>56</v>
-      </c>
-      <c r="L12" t="s">
-        <v>57</v>
-      </c>
-      <c r="M12" t="s">
-        <v>58</v>
-      </c>
-      <c r="N12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" t="s">
-        <v>26</v>
-      </c>
-      <c r="P12" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>26</v>
-      </c>
-      <c r="R12" t="s">
-        <v>55</v>
-      </c>
-      <c r="S12" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
@@ -1443,7 +1464,7 @@
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1464,10 +1485,10 @@
         <v>28</v>
       </c>
       <c r="K13" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" t="s">
         <v>61</v>
-      </c>
-      <c r="L13" t="s">
-        <v>57</v>
       </c>
       <c r="M13" t="s">
         <v>62</v>
@@ -1485,10 +1506,10 @@
         <v>26</v>
       </c>
       <c r="R13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -1502,7 +1523,7 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1523,10 +1544,10 @@
         <v>28</v>
       </c>
       <c r="K14" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L14" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M14" t="s">
         <v>66</v>
@@ -1538,13 +1559,13 @@
         <v>26</v>
       </c>
       <c r="P14" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>26</v>
+      </c>
+      <c r="R14" t="s">
         <v>59</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>26</v>
-      </c>
-      <c r="R14" t="s">
-        <v>55</v>
       </c>
       <c r="S14" t="s">
         <v>64</v>
@@ -1552,16 +1573,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1582,13 +1603,13 @@
         <v>28</v>
       </c>
       <c r="K15" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N15" t="s">
         <v>26</v>
@@ -1603,15 +1624,15 @@
         <v>26</v>
       </c>
       <c r="R15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
@@ -1620,7 +1641,7 @@
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1638,13 +1659,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M16" t="s">
         <v>73</v>
@@ -1656,16 +1677,16 @@
         <v>26</v>
       </c>
       <c r="P16" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>26</v>
+      </c>
+      <c r="R16" t="s">
         <v>59</v>
       </c>
-      <c r="Q16" t="s">
-        <v>26</v>
-      </c>
-      <c r="R16" t="s">
-        <v>55</v>
-      </c>
       <c r="S16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17">
@@ -1673,13 +1694,13 @@
         <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -1700,13 +1721,13 @@
         <v>43</v>
       </c>
       <c r="K17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N17" t="s">
         <v>26</v>
@@ -1715,13 +1736,13 @@
         <v>26</v>
       </c>
       <c r="P17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>26</v>
+      </c>
+      <c r="R17" t="s">
         <v>59</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>26</v>
-      </c>
-      <c r="R17" t="s">
-        <v>55</v>
       </c>
       <c r="S17" t="s">
         <v>74</v>
@@ -1729,16 +1750,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -1759,10 +1780,10 @@
         <v>43</v>
       </c>
       <c r="K18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L18" t="s">
         <v>76</v>
-      </c>
-      <c r="L18" t="s">
-        <v>72</v>
       </c>
       <c r="M18" t="s">
         <v>77</v>
@@ -1780,15 +1801,15 @@
         <v>26</v>
       </c>
       <c r="R18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
@@ -1797,7 +1818,7 @@
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
         <v>37</v>
@@ -1818,36 +1839,36 @@
         <v>43</v>
       </c>
       <c r="K19" t="s">
+        <v>80</v>
+      </c>
+      <c r="L19" t="s">
+        <v>81</v>
+      </c>
+      <c r="M19" t="s">
+        <v>82</v>
+      </c>
+      <c r="N19" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>26</v>
+      </c>
+      <c r="R19" t="s">
+        <v>59</v>
+      </c>
+      <c r="S19" t="s">
         <v>79</v>
-      </c>
-      <c r="L19" t="s">
-        <v>80</v>
-      </c>
-      <c r="M19" t="s">
-        <v>81</v>
-      </c>
-      <c r="N19" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" t="s">
-        <v>26</v>
-      </c>
-      <c r="P19" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>26</v>
-      </c>
-      <c r="R19" t="s">
-        <v>55</v>
-      </c>
-      <c r="S19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
@@ -1856,7 +1877,7 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
         <v>37</v>
@@ -1877,13 +1898,13 @@
         <v>43</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N20" t="s">
         <v>26</v>
@@ -1892,21 +1913,21 @@
         <v>26</v>
       </c>
       <c r="P20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q20" t="s">
         <v>26</v>
       </c>
       <c r="R20" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
@@ -1915,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
         <v>37</v>
@@ -1939,33 +1960,33 @@
         <v>44</v>
       </c>
       <c r="L21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M21" t="s">
+        <v>85</v>
+      </c>
+      <c r="N21" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>26</v>
+      </c>
+      <c r="R21" t="s">
+        <v>59</v>
+      </c>
+      <c r="S21" t="s">
         <v>84</v>
-      </c>
-      <c r="N21" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P21" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>26</v>
-      </c>
-      <c r="R21" t="s">
-        <v>55</v>
-      </c>
-      <c r="S21" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
@@ -1974,19 +1995,19 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
       </c>
       <c r="H22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s">
         <v>27</v>
@@ -1995,13 +2016,13 @@
         <v>28</v>
       </c>
       <c r="K22" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L22" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M22" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="N22" t="s">
         <v>26</v>
@@ -2010,7 +2031,7 @@
         <v>26</v>
       </c>
       <c r="P22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q22" t="s">
         <v>26</v>
@@ -2019,12 +2040,12 @@
         <v>34</v>
       </c>
       <c r="S22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
         <v>36</v>
@@ -2033,19 +2054,19 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s">
         <v>27</v>
@@ -2054,13 +2075,13 @@
         <v>28</v>
       </c>
       <c r="K23" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L23" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="N23" t="s">
         <v>26</v>
@@ -2069,7 +2090,7 @@
         <v>26</v>
       </c>
       <c r="P23" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q23" t="s">
         <v>26</v>
@@ -2078,12 +2099,12 @@
         <v>34</v>
       </c>
       <c r="S23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
         <v>20</v>
@@ -2092,19 +2113,19 @@
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
         <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
         <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s">
         <v>27</v>
@@ -2113,13 +2134,13 @@
         <v>28</v>
       </c>
       <c r="K24" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L24" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M24" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N24" t="s">
         <v>26</v>
@@ -2128,7 +2149,7 @@
         <v>26</v>
       </c>
       <c r="P24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q24" t="s">
         <v>26</v>
@@ -2137,12 +2158,12 @@
         <v>34</v>
       </c>
       <c r="S24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
@@ -2151,19 +2172,19 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
         <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
         <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s">
         <v>27</v>
@@ -2172,13 +2193,13 @@
         <v>28</v>
       </c>
       <c r="K25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L25" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M25" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N25" t="s">
         <v>26</v>
@@ -2187,7 +2208,7 @@
         <v>26</v>
       </c>
       <c r="P25" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q25" t="s">
         <v>26</v>
@@ -2196,12 +2217,12 @@
         <v>34</v>
       </c>
       <c r="S25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
         <v>20</v>
@@ -2210,19 +2231,19 @@
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
         <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s">
         <v>27</v>
@@ -2231,13 +2252,13 @@
         <v>43</v>
       </c>
       <c r="K26" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L26" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M26" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N26" t="s">
         <v>26</v>
@@ -2246,7 +2267,7 @@
         <v>26</v>
       </c>
       <c r="P26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q26" t="s">
         <v>26</v>
@@ -2255,12 +2276,12 @@
         <v>34</v>
       </c>
       <c r="S26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -2269,19 +2290,19 @@
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
         <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
       </c>
       <c r="H27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s">
         <v>27</v>
@@ -2290,13 +2311,13 @@
         <v>43</v>
       </c>
       <c r="K27" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L27" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M27" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N27" t="s">
         <v>26</v>
@@ -2305,7 +2326,7 @@
         <v>26</v>
       </c>
       <c r="P27" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q27" t="s">
         <v>26</v>
@@ -2314,12 +2335,12 @@
         <v>34</v>
       </c>
       <c r="S27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
         <v>20</v>
@@ -2328,57 +2349,57 @@
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s">
         <v>25</v>
       </c>
       <c r="H28" t="s">
+        <v>96</v>
+      </c>
+      <c r="I28" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" t="s">
+        <v>50</v>
+      </c>
+      <c r="K28" t="s">
+        <v>51</v>
+      </c>
+      <c r="L28" t="s">
+        <v>97</v>
+      </c>
+      <c r="M28" t="s">
+        <v>98</v>
+      </c>
+      <c r="N28" t="s">
+        <v>26</v>
+      </c>
+      <c r="O28" t="s">
+        <v>26</v>
+      </c>
+      <c r="P28" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>26</v>
+      </c>
+      <c r="R28" t="s">
+        <v>34</v>
+      </c>
+      <c r="S28" t="s">
         <v>95</v>
-      </c>
-      <c r="I28" t="s">
-        <v>27</v>
-      </c>
-      <c r="J28" t="s">
-        <v>28</v>
-      </c>
-      <c r="K28" t="s">
-        <v>56</v>
-      </c>
-      <c r="L28" t="s">
-        <v>65</v>
-      </c>
-      <c r="M28" t="s">
-        <v>66</v>
-      </c>
-      <c r="N28" t="s">
-        <v>26</v>
-      </c>
-      <c r="O28" t="s">
-        <v>26</v>
-      </c>
-      <c r="P28" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>26</v>
-      </c>
-      <c r="R28" t="s">
-        <v>34</v>
-      </c>
-      <c r="S28" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
@@ -2387,34 +2408,34 @@
         <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
         <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" t="s">
         <v>27</v>
       </c>
       <c r="J29" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K29" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L29" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="M29" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="N29" t="s">
         <v>26</v>
@@ -2423,7 +2444,7 @@
         <v>26</v>
       </c>
       <c r="P29" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q29" t="s">
         <v>26</v>
@@ -2432,12 +2453,12 @@
         <v>34</v>
       </c>
       <c r="S29" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
@@ -2446,19 +2467,19 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s">
         <v>25</v>
       </c>
       <c r="H30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" t="s">
         <v>27</v>
@@ -2467,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="K30" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L30" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="M30" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="N30" t="s">
         <v>26</v>
@@ -2482,7 +2503,7 @@
         <v>26</v>
       </c>
       <c r="P30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q30" t="s">
         <v>26</v>
@@ -2491,12 +2512,12 @@
         <v>34</v>
       </c>
       <c r="S30" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
         <v>36</v>
@@ -2505,19 +2526,19 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
       </c>
       <c r="H31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" t="s">
         <v>27</v>
@@ -2526,13 +2547,13 @@
         <v>28</v>
       </c>
       <c r="K31" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L31" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="M31" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="N31" t="s">
         <v>26</v>
@@ -2541,7 +2562,7 @@
         <v>26</v>
       </c>
       <c r="P31" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q31" t="s">
         <v>26</v>
@@ -2550,12 +2571,12 @@
         <v>34</v>
       </c>
       <c r="S31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
         <v>20</v>
@@ -2564,34 +2585,34 @@
         <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s">
         <v>25</v>
       </c>
       <c r="H32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" t="s">
         <v>27</v>
       </c>
       <c r="J32" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K32" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="L32" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="M32" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="N32" t="s">
         <v>26</v>
@@ -2600,7 +2621,7 @@
         <v>26</v>
       </c>
       <c r="P32" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q32" t="s">
         <v>26</v>
@@ -2609,12 +2630,12 @@
         <v>34</v>
       </c>
       <c r="S32" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
         <v>36</v>
@@ -2623,34 +2644,34 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E33" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s">
         <v>25</v>
       </c>
       <c r="H33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
         <v>27</v>
       </c>
       <c r="J33" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K33" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="L33" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="M33" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="N33" t="s">
         <v>26</v>
@@ -2659,7 +2680,7 @@
         <v>26</v>
       </c>
       <c r="P33" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q33" t="s">
         <v>26</v>
@@ -2668,33 +2689,33 @@
         <v>34</v>
       </c>
       <c r="S33" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E34" t="s">
         <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I34" t="s">
         <v>27</v>
@@ -2703,13 +2724,13 @@
         <v>43</v>
       </c>
       <c r="K34" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="L34" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M34" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="N34" t="s">
         <v>26</v>
@@ -2718,7 +2739,7 @@
         <v>26</v>
       </c>
       <c r="P34" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q34" t="s">
         <v>26</v>
@@ -2727,130 +2748,130 @@
         <v>34</v>
       </c>
       <c r="S34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s">
         <v>25</v>
       </c>
       <c r="H35" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I35" t="s">
         <v>27</v>
       </c>
       <c r="J35" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K35" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="L35" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="M35" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="N35" t="s">
+        <v>26</v>
+      </c>
+      <c r="O35" t="s">
+        <v>26</v>
+      </c>
+      <c r="P35" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>26</v>
+      </c>
+      <c r="R35" t="s">
+        <v>34</v>
+      </c>
+      <c r="S35" t="s">
         <v>105</v>
-      </c>
-      <c r="O35" t="s">
-        <v>26</v>
-      </c>
-      <c r="P35" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>26</v>
-      </c>
-      <c r="R35" t="s">
-        <v>34</v>
-      </c>
-      <c r="S35" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
         <v>36</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s">
         <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="I36" t="s">
         <v>27</v>
       </c>
       <c r="J36" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K36" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="L36" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="M36" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="N36" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="O36" t="s">
         <v>26</v>
       </c>
       <c r="P36" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>26</v>
+      </c>
+      <c r="R36" t="s">
+        <v>34</v>
+      </c>
+      <c r="S36" t="s">
         <v>106</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>26</v>
-      </c>
-      <c r="R36" t="s">
-        <v>34</v>
-      </c>
-      <c r="S36" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s">
         <v>20</v>
@@ -2859,13 +2880,13 @@
         <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F37" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G37" t="s">
         <v>25</v>
@@ -2880,22 +2901,22 @@
         <v>28</v>
       </c>
       <c r="K37" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L37" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M37" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N37" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="O37" t="s">
         <v>26</v>
       </c>
       <c r="P37" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="Q37" t="s">
         <v>26</v>
@@ -2904,12 +2925,12 @@
         <v>34</v>
       </c>
       <c r="S37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
         <v>36</v>
@@ -2918,13 +2939,13 @@
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G38" t="s">
         <v>25</v>
@@ -2939,22 +2960,22 @@
         <v>28</v>
       </c>
       <c r="K38" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L38" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M38" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N38" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="O38" t="s">
         <v>26</v>
       </c>
       <c r="P38" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="Q38" t="s">
         <v>26</v>
@@ -2963,12 +2984,12 @@
         <v>34</v>
       </c>
       <c r="S38" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
         <v>20</v>
@@ -2983,7 +3004,7 @@
         <v>23</v>
       </c>
       <c r="F39" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G39" t="s">
         <v>25</v>
@@ -2995,16 +3016,16 @@
         <v>27</v>
       </c>
       <c r="J39" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K39" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="L39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M39" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N39" t="s">
         <v>32</v>
@@ -3013,7 +3034,7 @@
         <v>26</v>
       </c>
       <c r="P39" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q39" t="s">
         <v>26</v>
@@ -3022,12 +3043,12 @@
         <v>34</v>
       </c>
       <c r="S39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
         <v>36</v>
@@ -3042,7 +3063,7 @@
         <v>23</v>
       </c>
       <c r="F40" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G40" t="s">
         <v>25</v>
@@ -3054,16 +3075,16 @@
         <v>27</v>
       </c>
       <c r="J40" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K40" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="L40" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M40" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N40" t="s">
         <v>32</v>
@@ -3072,7 +3093,7 @@
         <v>26</v>
       </c>
       <c r="P40" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q40" t="s">
         <v>26</v>
@@ -3081,12 +3102,12 @@
         <v>34</v>
       </c>
       <c r="S40" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s">
         <v>20</v>
@@ -3101,7 +3122,7 @@
         <v>23</v>
       </c>
       <c r="F41" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
@@ -3116,10 +3137,10 @@
         <v>43</v>
       </c>
       <c r="K41" t="s">
+        <v>75</v>
+      </c>
+      <c r="L41" t="s">
         <v>76</v>
-      </c>
-      <c r="L41" t="s">
-        <v>72</v>
       </c>
       <c r="M41" t="s">
         <v>77</v>
@@ -3140,12 +3161,12 @@
         <v>34</v>
       </c>
       <c r="S41" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
         <v>36</v>
@@ -3160,7 +3181,7 @@
         <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
@@ -3175,10 +3196,10 @@
         <v>43</v>
       </c>
       <c r="K42" t="s">
+        <v>75</v>
+      </c>
+      <c r="L42" t="s">
         <v>76</v>
-      </c>
-      <c r="L42" t="s">
-        <v>72</v>
       </c>
       <c r="M42" t="s">
         <v>77</v>
@@ -3199,12 +3220,12 @@
         <v>34</v>
       </c>
       <c r="S42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
         <v>20</v>
@@ -3219,7 +3240,7 @@
         <v>23</v>
       </c>
       <c r="F43" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G43" t="s">
         <v>25</v>
@@ -3234,13 +3255,13 @@
         <v>43</v>
       </c>
       <c r="K43" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="L43" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M43" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N43" t="s">
         <v>32</v>
@@ -3249,7 +3270,7 @@
         <v>26</v>
       </c>
       <c r="P43" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="Q43" t="s">
         <v>26</v>
@@ -3258,12 +3279,12 @@
         <v>34</v>
       </c>
       <c r="S43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B44" t="s">
         <v>36</v>
@@ -3278,7 +3299,7 @@
         <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G44" t="s">
         <v>25</v>
@@ -3293,13 +3314,13 @@
         <v>43</v>
       </c>
       <c r="K44" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="L44" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M44" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N44" t="s">
         <v>32</v>
@@ -3308,7 +3329,7 @@
         <v>26</v>
       </c>
       <c r="P44" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="Q44" t="s">
         <v>26</v>
@@ -3317,12 +3338,12 @@
         <v>34</v>
       </c>
       <c r="S44" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B45" t="s">
         <v>20</v>
@@ -3331,13 +3352,13 @@
         <v>47</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G45" t="s">
         <v>25</v>
@@ -3349,25 +3370,25 @@
         <v>27</v>
       </c>
       <c r="J45" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K45" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="L45" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="M45" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="N45" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="O45" t="s">
         <v>26</v>
       </c>
       <c r="P45" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="Q45" t="s">
         <v>26</v>
@@ -3376,12 +3397,12 @@
         <v>34</v>
       </c>
       <c r="S45" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B46" t="s">
         <v>36</v>
@@ -3390,13 +3411,13 @@
         <v>47</v>
       </c>
       <c r="D46" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
         <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G46" t="s">
         <v>25</v>
@@ -3408,25 +3429,25 @@
         <v>27</v>
       </c>
       <c r="J46" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K46" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="L46" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="M46" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="N46" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="O46" t="s">
         <v>26</v>
       </c>
       <c r="P46" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="Q46" t="s">
         <v>26</v>
@@ -3435,12 +3456,12 @@
         <v>34</v>
       </c>
       <c r="S46" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B47" t="s">
         <v>20</v>
@@ -3449,13 +3470,13 @@
         <v>47</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E47" t="s">
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G47" t="s">
         <v>25</v>
@@ -3470,22 +3491,22 @@
         <v>28</v>
       </c>
       <c r="K47" t="s">
+        <v>60</v>
+      </c>
+      <c r="L47" t="s">
         <v>61</v>
-      </c>
-      <c r="L47" t="s">
-        <v>57</v>
       </c>
       <c r="M47" t="s">
         <v>62</v>
       </c>
       <c r="N47" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O47" t="s">
         <v>26</v>
       </c>
       <c r="P47" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="Q47" t="s">
         <v>26</v>
@@ -3494,12 +3515,12 @@
         <v>34</v>
       </c>
       <c r="S47" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
         <v>36</v>
@@ -3508,13 +3529,13 @@
         <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E48" t="s">
         <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G48" t="s">
         <v>25</v>
@@ -3529,22 +3550,22 @@
         <v>28</v>
       </c>
       <c r="K48" t="s">
+        <v>60</v>
+      </c>
+      <c r="L48" t="s">
         <v>61</v>
-      </c>
-      <c r="L48" t="s">
-        <v>57</v>
       </c>
       <c r="M48" t="s">
         <v>62</v>
       </c>
       <c r="N48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O48" t="s">
         <v>26</v>
       </c>
       <c r="P48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="Q48" t="s">
         <v>26</v>
@@ -3553,12 +3574,12 @@
         <v>34</v>
       </c>
       <c r="S48" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
@@ -3567,13 +3588,13 @@
         <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E49" t="s">
         <v>23</v>
       </c>
       <c r="F49" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G49" t="s">
         <v>25</v>
@@ -3588,22 +3609,22 @@
         <v>28</v>
       </c>
       <c r="K49" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L49" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M49" t="s">
         <v>66</v>
       </c>
       <c r="N49" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O49" t="s">
         <v>26</v>
       </c>
       <c r="P49" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="Q49" t="s">
         <v>26</v>
@@ -3612,12 +3633,12 @@
         <v>34</v>
       </c>
       <c r="S49" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B50" t="s">
         <v>36</v>
@@ -3626,13 +3647,13 @@
         <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E50" t="s">
         <v>23</v>
       </c>
       <c r="F50" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G50" t="s">
         <v>25</v>
@@ -3647,22 +3668,22 @@
         <v>28</v>
       </c>
       <c r="K50" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L50" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M50" t="s">
         <v>66</v>
       </c>
       <c r="N50" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O50" t="s">
         <v>26</v>
       </c>
       <c r="P50" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="Q50" t="s">
         <v>26</v>
@@ -3671,12 +3692,12 @@
         <v>34</v>
       </c>
       <c r="S50" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
@@ -3685,13 +3706,13 @@
         <v>47</v>
       </c>
       <c r="D51" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E51" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G51" t="s">
         <v>25</v>
@@ -3706,22 +3727,22 @@
         <v>28</v>
       </c>
       <c r="K51" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L51" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N51" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O51" t="s">
         <v>26</v>
       </c>
       <c r="P51" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="Q51" t="s">
         <v>26</v>
@@ -3730,12 +3751,12 @@
         <v>34</v>
       </c>
       <c r="S51" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B52" t="s">
         <v>36</v>
@@ -3744,13 +3765,13 @@
         <v>47</v>
       </c>
       <c r="D52" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E52" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F52" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G52" t="s">
         <v>25</v>
@@ -3765,22 +3786,22 @@
         <v>28</v>
       </c>
       <c r="K52" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L52" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N52" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O52" t="s">
         <v>26</v>
       </c>
       <c r="P52" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="Q52" t="s">
         <v>26</v>
@@ -3789,12 +3810,12 @@
         <v>34</v>
       </c>
       <c r="S52" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B53" t="s">
         <v>20</v>
@@ -3803,13 +3824,13 @@
         <v>47</v>
       </c>
       <c r="D53" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E53" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F53" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
@@ -3821,25 +3842,25 @@
         <v>27</v>
       </c>
       <c r="J53" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K53" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L53" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M53" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N53" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O53" t="s">
         <v>26</v>
       </c>
       <c r="P53" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="Q53" t="s">
         <v>26</v>
@@ -3848,12 +3869,12 @@
         <v>34</v>
       </c>
       <c r="S53" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B54" t="s">
         <v>36</v>
@@ -3862,13 +3883,13 @@
         <v>47</v>
       </c>
       <c r="D54" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E54" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F54" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G54" t="s">
         <v>25</v>
@@ -3880,25 +3901,25 @@
         <v>27</v>
       </c>
       <c r="J54" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K54" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L54" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M54" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N54" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O54" t="s">
         <v>26</v>
       </c>
       <c r="P54" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="Q54" t="s">
         <v>26</v>
@@ -3907,27 +3928,27 @@
         <v>34</v>
       </c>
       <c r="S54" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C55" t="s">
         <v>47</v>
       </c>
       <c r="D55" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G55" t="s">
         <v>25</v>
@@ -3942,22 +3963,22 @@
         <v>43</v>
       </c>
       <c r="K55" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="L55" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M55" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="N55" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O55" t="s">
         <v>26</v>
       </c>
       <c r="P55" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="Q55" t="s">
         <v>26</v>
@@ -3966,7 +3987,125 @@
         <v>34</v>
       </c>
       <c r="S55" t="s">
-        <v>127</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>133</v>
+      </c>
+      <c r="B56" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" t="s">
+        <v>108</v>
+      </c>
+      <c r="E56" t="s">
+        <v>37</v>
+      </c>
+      <c r="F56" t="s">
+        <v>109</v>
+      </c>
+      <c r="G56" t="s">
+        <v>25</v>
+      </c>
+      <c r="H56" t="s">
+        <v>26</v>
+      </c>
+      <c r="I56" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" t="s">
+        <v>43</v>
+      </c>
+      <c r="K56" t="s">
+        <v>118</v>
+      </c>
+      <c r="L56" t="s">
+        <v>76</v>
+      </c>
+      <c r="M56" t="s">
+        <v>119</v>
+      </c>
+      <c r="N56" t="s">
+        <v>110</v>
+      </c>
+      <c r="O56" t="s">
+        <v>26</v>
+      </c>
+      <c r="P56" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>26</v>
+      </c>
+      <c r="R56" t="s">
+        <v>34</v>
+      </c>
+      <c r="S56" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" t="s">
+        <v>108</v>
+      </c>
+      <c r="E57" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57" t="s">
+        <v>109</v>
+      </c>
+      <c r="G57" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" t="s">
+        <v>43</v>
+      </c>
+      <c r="K57" t="s">
+        <v>75</v>
+      </c>
+      <c r="L57" t="s">
+        <v>76</v>
+      </c>
+      <c r="M57" t="s">
+        <v>77</v>
+      </c>
+      <c r="N57" t="s">
+        <v>110</v>
+      </c>
+      <c r="O57" t="s">
+        <v>26</v>
+      </c>
+      <c r="P57" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>26</v>
+      </c>
+      <c r="R57" t="s">
+        <v>34</v>
+      </c>
+      <c r="S57" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
